--- a/data/trans_orig/Q03B_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q03B_R-Provincia-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,0</t>
+          <t>0,8; 1,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,78</t>
+          <t>1,35; 1,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 1,82</t>
+          <t>1,44; 1,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 2,81</t>
+          <t>2,38; 2,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 4,57</t>
+          <t>3,92; 4,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 3,87</t>
+          <t>3,27; 3,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 1,86</t>
+          <t>1,6; 1,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 3,11</t>
+          <t>2,66; 3,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 2,81</t>
+          <t>2,41; 2,8</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,01</t>
+          <t>1,63; 2,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -797,37 +797,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,48</t>
+          <t>1,23; 1,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 4,63</t>
+          <t>4,2; 4,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 3,92</t>
+          <t>3,53; 3,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 3,87</t>
+          <t>3,52; 3,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 3,31</t>
+          <t>2,97; 3,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 2,6</t>
+          <t>2,33; 2,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 2,72</t>
+          <t>2,47; 2,73</t>
         </is>
       </c>
     </row>
@@ -897,27 +897,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,78</t>
+          <t>0,57; 0,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,32</t>
+          <t>1,04; 1,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 1,89</t>
+          <t>1,57; 1,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 3,29</t>
+          <t>2,79; 3,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 3,28</t>
+          <t>2,88; 3,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,17 +927,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,04</t>
+          <t>1,71; 2,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 2,3</t>
+          <t>2,02; 2,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 2,46</t>
+          <t>2,22; 2,44</t>
         </is>
       </c>
     </row>
@@ -1007,32 +1007,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,88</t>
+          <t>0,65; 0,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,08</t>
+          <t>1,7; 2,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 1,91</t>
+          <t>1,62; 1,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 3,08</t>
+          <t>2,66; 3,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 4,57</t>
+          <t>4,04; 4,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 3,68</t>
+          <t>3,25; 3,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 3,33</t>
+          <t>2,93; 3,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 2,78</t>
+          <t>2,46; 2,77</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,65</t>
+          <t>1,16; 1,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1127,37 +1127,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,2</t>
+          <t>1,83; 2,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 4,53</t>
+          <t>3,85; 4,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 3,8</t>
+          <t>3,22; 3,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 5,22</t>
+          <t>4,7; 5,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 3,08</t>
+          <t>2,56; 3,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 2,47</t>
+          <t>2,03; 2,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 3,74</t>
+          <t>3,29; 3,72</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,92</t>
+          <t>0,63; 0,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,4</t>
+          <t>1,05; 1,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,15</t>
+          <t>1,76; 2,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,74; 3,2</t>
+          <t>2,73; 3,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,11; 3,62</t>
+          <t>3,13; 3,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,4; 3,86</t>
+          <t>3,4; 3,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,08</t>
+          <t>1,75; 2,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 2,48</t>
+          <t>2,12; 2,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 2,97</t>
+          <t>2,63; 2,97</t>
         </is>
       </c>
     </row>
@@ -1337,37 +1337,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,05</t>
+          <t>1,63; 2,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,43</t>
+          <t>1,23; 1,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 1,72</t>
+          <t>1,38; 1,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,59; 3,97</t>
+          <t>3,58; 3,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,16</t>
+          <t>2,86; 3,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,18</t>
+          <t>2,83; 3,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 2,96</t>
+          <t>2,68; 2,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 2,42</t>
+          <t>2,18; 2,43</t>
         </is>
       </c>
     </row>
@@ -1447,42 +1447,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,36</t>
+          <t>1,08; 1,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,0</t>
+          <t>1,74; 1,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,77; 1,94</t>
+          <t>1,78; 1,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,57; 3,94</t>
+          <t>3,56; 3,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,27; 3,58</t>
+          <t>3,29; 3,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,34; 3,59</t>
+          <t>3,35; 3,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,37; 2,64</t>
+          <t>2,36; 2,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,56; 2,78</t>
+          <t>2,58; 2,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,33</t>
+          <t>1,2; 1,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,47; 3,64</t>
+          <t>3,47; 3,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,4; 3,54</t>
+          <t>3,39; 3,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,57; 2,67</t>
+          <t>2,57; 2,66</t>
         </is>
       </c>
     </row>
